--- a/inputs/AddictO_Product_Defs.xlsx
+++ b/inputs/AddictO_Product_Defs.xlsx
@@ -949,83 +949,83 @@
       <c r="AC7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000208</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Clinical Research Support System</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>A chemical measurement device that measures the amount of some smoke constituent produced by puffing on a cigarette.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>chemical measurement device</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>A device for measuring the chemicals ingested when puffing on a cigarette.</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="7" t="inlineStr"/>
+      <c r="V8" s="7" t="inlineStr"/>
+      <c r="W8" s="7" t="inlineStr"/>
+      <c r="X8" s="7" t="inlineStr"/>
+      <c r="Y8" s="7" t="inlineStr"/>
+      <c r="Z8" s="7" t="inlineStr"/>
+      <c r="AA8" s="7" t="inlineStr"/>
+      <c r="AB8" s="7" t="inlineStr">
         <is>
           <t>CReSS</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AC8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1679,75 +1679,75 @@
       <c r="AC17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001242</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Marketing that consists of paid-for messaging.</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr"/>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="7" t="inlineStr"/>
+      <c r="V18" s="7" t="inlineStr"/>
+      <c r="W18" s="7" t="inlineStr"/>
+      <c r="X18" s="7" t="inlineStr"/>
+      <c r="Y18" s="7" t="inlineStr"/>
+      <c r="Z18" s="7" t="inlineStr"/>
+      <c r="AA18" s="7" t="inlineStr"/>
+      <c r="AB18" s="7" t="inlineStr"/>
+      <c r="AC18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15695,79 +15695,79 @@
       <c r="AC215" s="7" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000186</t>
         </is>
       </c>
-      <c r="B216" s="3" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>individual-level harm to health of product use</t>
         </is>
       </c>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="C216" s="7" t="inlineStr">
         <is>
           <t>Individual-level harm of product use where the harm is to health.</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D216" s="7" t="inlineStr">
         <is>
           <t>individual-level harm of product use</t>
         </is>
       </c>
-      <c r="E216" s="3" t="inlineStr">
+      <c r="E216" s="7" t="inlineStr">
         <is>
           <t>occurrent</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr"/>
-      <c r="H216" s="3" t="inlineStr"/>
-      <c r="I216" s="3" t="n">
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr"/>
+      <c r="H216" s="7" t="inlineStr"/>
+      <c r="I216" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J216" s="3" t="n">
+      <c r="J216" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K216" s="3" t="inlineStr">
+      <c r="K216" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Because what constitutes harm needs to be operationalised. </t>
         </is>
       </c>
-      <c r="L216" s="3" t="inlineStr">
+      <c r="L216" s="7" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="M216" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N216" s="3" t="inlineStr"/>
-      <c r="O216" s="3" t="inlineStr"/>
-      <c r="P216" s="3" t="inlineStr">
+      <c r="M216" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N216" s="7" t="inlineStr"/>
+      <c r="O216" s="7" t="inlineStr"/>
+      <c r="P216" s="7" t="inlineStr">
         <is>
           <t>The harm to health caused to an individual from their use of a product.</t>
         </is>
       </c>
-      <c r="Q216" s="3" t="inlineStr"/>
-      <c r="R216" s="3" t="inlineStr"/>
-      <c r="S216" s="3" t="inlineStr"/>
-      <c r="T216" s="3" t="inlineStr"/>
-      <c r="U216" s="3" t="inlineStr"/>
-      <c r="V216" s="3" t="inlineStr"/>
-      <c r="W216" s="3" t="inlineStr"/>
-      <c r="X216" s="3" t="inlineStr"/>
-      <c r="Y216" s="3" t="inlineStr"/>
-      <c r="Z216" s="3" t="inlineStr"/>
-      <c r="AA216" s="3" t="inlineStr"/>
-      <c r="AB216" s="3" t="inlineStr"/>
-      <c r="AC216" s="3" t="inlineStr"/>
+      <c r="Q216" s="7" t="inlineStr"/>
+      <c r="R216" s="7" t="inlineStr"/>
+      <c r="S216" s="7" t="inlineStr"/>
+      <c r="T216" s="7" t="inlineStr"/>
+      <c r="U216" s="7" t="inlineStr"/>
+      <c r="V216" s="7" t="inlineStr"/>
+      <c r="W216" s="7" t="inlineStr"/>
+      <c r="X216" s="7" t="inlineStr"/>
+      <c r="Y216" s="7" t="inlineStr"/>
+      <c r="Z216" s="7" t="inlineStr"/>
+      <c r="AA216" s="7" t="inlineStr"/>
+      <c r="AB216" s="7" t="inlineStr"/>
+      <c r="AC216" s="7" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -30680,75 +30680,75 @@
       <c r="AC432" s="5" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="3" t="inlineStr">
+      <c r="A433" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001246</t>
         </is>
       </c>
-      <c r="B433" s="3" t="inlineStr">
+      <c r="B433" s="7" t="inlineStr">
         <is>
           <t>tobacco marketing</t>
         </is>
       </c>
-      <c r="C433" s="3" t="inlineStr">
+      <c r="C433" s="7" t="inlineStr">
         <is>
           <t>Marketing of a tobacco-containing product.</t>
         </is>
       </c>
-      <c r="D433" s="3" t="inlineStr">
+      <c r="D433" s="7" t="inlineStr">
         <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="E433" s="3" t="inlineStr">
+      <c r="E433" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="F433" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G433" s="3" t="inlineStr"/>
-      <c r="H433" s="3" t="inlineStr"/>
-      <c r="I433" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J433" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K433" s="3" t="inlineStr"/>
-      <c r="L433" s="3" t="inlineStr">
+      <c r="F433" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G433" s="7" t="inlineStr"/>
+      <c r="H433" s="7" t="inlineStr"/>
+      <c r="I433" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J433" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K433" s="7" t="inlineStr"/>
+      <c r="L433" s="7" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="M433" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N433" s="3" t="inlineStr"/>
-      <c r="O433" s="3" t="inlineStr"/>
-      <c r="P433" s="3" t="inlineStr"/>
-      <c r="Q433" s="3" t="inlineStr"/>
-      <c r="R433" s="3" t="inlineStr"/>
-      <c r="S433" s="3" t="inlineStr"/>
-      <c r="T433" s="3" t="inlineStr"/>
-      <c r="U433" s="3" t="inlineStr"/>
-      <c r="V433" s="3" t="inlineStr"/>
-      <c r="W433" s="3" t="inlineStr"/>
-      <c r="X433" s="3" t="inlineStr"/>
-      <c r="Y433" s="3" t="inlineStr"/>
-      <c r="Z433" s="3" t="inlineStr"/>
-      <c r="AA433" s="3" t="inlineStr"/>
-      <c r="AB433" s="3" t="inlineStr"/>
-      <c r="AC433" s="3" t="inlineStr"/>
+      <c r="M433" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N433" s="7" t="inlineStr"/>
+      <c r="O433" s="7" t="inlineStr"/>
+      <c r="P433" s="7" t="inlineStr"/>
+      <c r="Q433" s="7" t="inlineStr"/>
+      <c r="R433" s="7" t="inlineStr"/>
+      <c r="S433" s="7" t="inlineStr"/>
+      <c r="T433" s="7" t="inlineStr"/>
+      <c r="U433" s="7" t="inlineStr"/>
+      <c r="V433" s="7" t="inlineStr"/>
+      <c r="W433" s="7" t="inlineStr"/>
+      <c r="X433" s="7" t="inlineStr"/>
+      <c r="Y433" s="7" t="inlineStr"/>
+      <c r="Z433" s="7" t="inlineStr"/>
+      <c r="AA433" s="7" t="inlineStr"/>
+      <c r="AB433" s="7" t="inlineStr"/>
+      <c r="AC433" s="7" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="4" t="inlineStr">

--- a/inputs/AddictO_Product_Defs.xlsx
+++ b/inputs/AddictO_Product_Defs.xlsx
@@ -7091,75 +7091,75 @@
       <c r="AC94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0001243</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>cinema advertising</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Advertising that consists of video images shown in a cinema.</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="3" t="inlineStr"/>
-      <c r="P95" s="3" t="inlineStr"/>
-      <c r="Q95" s="3" t="inlineStr"/>
-      <c r="R95" s="3" t="inlineStr"/>
-      <c r="S95" s="3" t="inlineStr"/>
-      <c r="T95" s="3" t="inlineStr"/>
-      <c r="U95" s="3" t="inlineStr"/>
-      <c r="V95" s="3" t="inlineStr"/>
-      <c r="W95" s="3" t="inlineStr"/>
-      <c r="X95" s="3" t="inlineStr"/>
-      <c r="Y95" s="3" t="inlineStr"/>
-      <c r="Z95" s="3" t="inlineStr"/>
-      <c r="AA95" s="3" t="inlineStr"/>
-      <c r="AB95" s="3" t="inlineStr"/>
-      <c r="AC95" s="3" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="7" t="inlineStr"/>
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="inlineStr"/>
+      <c r="R95" s="7" t="inlineStr"/>
+      <c r="S95" s="7" t="inlineStr"/>
+      <c r="T95" s="7" t="inlineStr"/>
+      <c r="U95" s="7" t="inlineStr"/>
+      <c r="V95" s="7" t="inlineStr"/>
+      <c r="W95" s="7" t="inlineStr"/>
+      <c r="X95" s="7" t="inlineStr"/>
+      <c r="Y95" s="7" t="inlineStr"/>
+      <c r="Z95" s="7" t="inlineStr"/>
+      <c r="AA95" s="7" t="inlineStr"/>
+      <c r="AB95" s="7" t="inlineStr"/>
+      <c r="AC95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -30257,73 +30257,73 @@
       <c r="AC426" s="4" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="3" t="inlineStr">
+      <c r="A427" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000306</t>
         </is>
       </c>
-      <c r="B427" s="3" t="inlineStr">
+      <c r="B427" s="7" t="inlineStr">
         <is>
           <t>tobacco advertising</t>
         </is>
       </c>
-      <c r="C427" s="3" t="inlineStr">
+      <c r="C427" s="7" t="inlineStr">
         <is>
           <t>Advertising of a tobacco-containing product.</t>
         </is>
       </c>
-      <c r="D427" s="3" t="inlineStr">
+      <c r="D427" s="7" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="E427" s="3" t="inlineStr">
+      <c r="E427" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="F427" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G427" s="3" t="inlineStr"/>
-      <c r="H427" s="3" t="inlineStr"/>
-      <c r="I427" s="3" t="n">
+      <c r="F427" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G427" s="7" t="inlineStr"/>
+      <c r="H427" s="7" t="inlineStr"/>
+      <c r="I427" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J427" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K427" s="3" t="inlineStr"/>
-      <c r="L427" s="3" t="inlineStr">
+      <c r="J427" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K427" s="7" t="inlineStr"/>
+      <c r="L427" s="7" t="inlineStr">
         <is>
           <t>SC;JH; RW</t>
         </is>
       </c>
-      <c r="M427" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N427" s="3" t="inlineStr"/>
-      <c r="O427" s="3" t="inlineStr"/>
-      <c r="P427" s="3" t="inlineStr"/>
-      <c r="Q427" s="3" t="inlineStr"/>
-      <c r="R427" s="3" t="inlineStr"/>
-      <c r="S427" s="3" t="inlineStr"/>
-      <c r="T427" s="3" t="inlineStr"/>
-      <c r="U427" s="3" t="inlineStr"/>
-      <c r="V427" s="3" t="inlineStr"/>
-      <c r="W427" s="3" t="inlineStr"/>
-      <c r="X427" s="3" t="inlineStr"/>
-      <c r="Y427" s="3" t="inlineStr"/>
-      <c r="Z427" s="3" t="inlineStr"/>
-      <c r="AA427" s="3" t="inlineStr"/>
-      <c r="AB427" s="3" t="inlineStr"/>
-      <c r="AC427" s="3" t="inlineStr"/>
+      <c r="M427" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N427" s="7" t="inlineStr"/>
+      <c r="O427" s="7" t="inlineStr"/>
+      <c r="P427" s="7" t="inlineStr"/>
+      <c r="Q427" s="7" t="inlineStr"/>
+      <c r="R427" s="7" t="inlineStr"/>
+      <c r="S427" s="7" t="inlineStr"/>
+      <c r="T427" s="7" t="inlineStr"/>
+      <c r="U427" s="7" t="inlineStr"/>
+      <c r="V427" s="7" t="inlineStr"/>
+      <c r="W427" s="7" t="inlineStr"/>
+      <c r="X427" s="7" t="inlineStr"/>
+      <c r="Y427" s="7" t="inlineStr"/>
+      <c r="Z427" s="7" t="inlineStr"/>
+      <c r="AA427" s="7" t="inlineStr"/>
+      <c r="AB427" s="7" t="inlineStr"/>
+      <c r="AC427" s="7" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="5" t="inlineStr">

--- a/inputs/AddictO_Product_Defs.xlsx
+++ b/inputs/AddictO_Product_Defs.xlsx
@@ -7162,73 +7162,73 @@
       <c r="AC95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000894</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>cinema tobacco advertising</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Cinema advertising of a tobacco product.</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>cinema advertising</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="3" t="n">
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
-      <c r="L96" s="3" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K96" s="7" t="inlineStr"/>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>KS; RW</t>
         </is>
       </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr"/>
-      <c r="O96" s="3" t="inlineStr"/>
-      <c r="P96" s="3" t="inlineStr"/>
-      <c r="Q96" s="3" t="inlineStr"/>
-      <c r="R96" s="3" t="inlineStr"/>
-      <c r="S96" s="3" t="inlineStr"/>
-      <c r="T96" s="3" t="inlineStr"/>
-      <c r="U96" s="3" t="inlineStr"/>
-      <c r="V96" s="3" t="inlineStr"/>
-      <c r="W96" s="3" t="inlineStr"/>
-      <c r="X96" s="3" t="inlineStr"/>
-      <c r="Y96" s="3" t="inlineStr"/>
-      <c r="Z96" s="3" t="inlineStr"/>
-      <c r="AA96" s="3" t="inlineStr"/>
-      <c r="AB96" s="3" t="inlineStr"/>
-      <c r="AC96" s="3" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr"/>
+      <c r="O96" s="7" t="inlineStr"/>
+      <c r="P96" s="7" t="inlineStr"/>
+      <c r="Q96" s="7" t="inlineStr"/>
+      <c r="R96" s="7" t="inlineStr"/>
+      <c r="S96" s="7" t="inlineStr"/>
+      <c r="T96" s="7" t="inlineStr"/>
+      <c r="U96" s="7" t="inlineStr"/>
+      <c r="V96" s="7" t="inlineStr"/>
+      <c r="W96" s="7" t="inlineStr"/>
+      <c r="X96" s="7" t="inlineStr"/>
+      <c r="Y96" s="7" t="inlineStr"/>
+      <c r="Z96" s="7" t="inlineStr"/>
+      <c r="AA96" s="7" t="inlineStr"/>
+      <c r="AB96" s="7" t="inlineStr"/>
+      <c r="AC96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
